--- a/moduli_aziende/aifecs/moduli_compilati/MOD-530-C-Matrice_Responsabilita.xlsx
+++ b/moduli_aziende/aifecs/moduli_compilati/MOD-530-C-Matrice_Responsabilita.xlsx
@@ -2,26 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R67feb5c493944b85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R031a96421bf34f67"/>
   </x:sheets>
 </x:workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:comments xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:authors>
-    <x:author/>
-  </x:authors>
-  <x:commentList>
-    <x:comment ref="A1" authorId="0">
-      <x:text>
-        <x:r>
-          <x:t>AIFECS — BOZZA DA CONFERMARE. Proposta operativa per il sistema qualità ISO 9001. Ruoli, priorità, criteri e obiettivi sono proposte. I registri vanno compilati con dati ed evidenze reali. Vedere la guida e la proposta operativa del pacchetto.</x:t>
-        </x:r>
-      </x:text>
-    </x:comment>
-  </x:commentList>
-</x:comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -353,9 +336,7 @@
       <x:c r="D2" s="6" t="str">
         <x:v>DIR / QUAL</x:v>
       </x:c>
-      <x:c r="E2" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E2" s="6"/>
     </x:row>
     <x:row r="3" ht="50" customHeight="1">
       <x:c r="A3" s="6" t="str">
@@ -370,9 +351,7 @@
       <x:c r="D3" s="6" t="str">
         <x:v>DIR</x:v>
       </x:c>
-      <x:c r="E3" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E3" s="6"/>
     </x:row>
     <x:row r="4" ht="50" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -387,9 +366,7 @@
       <x:c r="D4" s="6" t="str">
         <x:v>DIR / QUAL</x:v>
       </x:c>
-      <x:c r="E4" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E4" s="6"/>
     </x:row>
     <x:row r="5" ht="50" customHeight="1">
       <x:c r="A5" s="6" t="str">
@@ -399,14 +376,12 @@
         <x:v>Analisi e trattamento rischi</x:v>
       </x:c>
       <x:c r="C5" s="6" t="str">
-        <x:v>MOD-610-B</x:v>
+        <x:v>MOD-610-B / Mod.01.PO.06.1_VR / Mod.02.PO.06.1_Risk_management</x:v>
       </x:c>
       <x:c r="D5" s="6" t="str">
         <x:v>DIR / QUAL / DID</x:v>
       </x:c>
-      <x:c r="E5" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E5" s="6"/>
     </x:row>
     <x:row r="6" ht="50" customHeight="1">
       <x:c r="A6" s="6" t="str">
@@ -421,9 +396,7 @@
       <x:c r="D6" s="6" t="str">
         <x:v>DIR / QUAL</x:v>
       </x:c>
-      <x:c r="E6" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E6" s="6"/>
     </x:row>
     <x:row r="7" ht="50" customHeight="1">
       <x:c r="A7" s="6" t="str">
@@ -438,9 +411,7 @@
       <x:c r="D7" s="6" t="str">
         <x:v>SOC</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E7" s="6"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="6" t="str">
@@ -455,9 +426,7 @@
       <x:c r="D8" s="6" t="str">
         <x:v>DIR / SOC</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E8" s="6"/>
     </x:row>
     <x:row r="9" ht="50" customHeight="1">
       <x:c r="A9" s="6" t="str">
@@ -472,9 +441,7 @@
       <x:c r="D9" s="6" t="str">
         <x:v>SOC / QUAL</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E9" s="6"/>
     </x:row>
     <x:row r="10" ht="50" customHeight="1">
       <x:c r="A10" s="6" t="str">
@@ -489,9 +456,7 @@
       <x:c r="D10" s="6" t="str">
         <x:v>DID / SEG</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E10" s="6"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="6" t="str">
@@ -506,9 +471,7 @@
       <x:c r="D11" s="6" t="str">
         <x:v>DID</x:v>
       </x:c>
-      <x:c r="E11" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E11" s="6"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="6" t="str">
@@ -523,9 +486,7 @@
       <x:c r="D12" s="6" t="str">
         <x:v>DID</x:v>
       </x:c>
-      <x:c r="E12" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E12" s="6"/>
     </x:row>
     <x:row r="13" ht="50" customHeight="1">
       <x:c r="A13" s="6" t="str">
@@ -540,9 +501,7 @@
       <x:c r="D13" s="6" t="str">
         <x:v>DID</x:v>
       </x:c>
-      <x:c r="E13" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E13" s="6"/>
     </x:row>
     <x:row r="14" ht="50" customHeight="1">
       <x:c r="A14" s="6" t="str">
@@ -557,9 +516,7 @@
       <x:c r="D14" s="6" t="str">
         <x:v>DID</x:v>
       </x:c>
-      <x:c r="E14" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E14" s="6"/>
     </x:row>
     <x:row r="15" ht="50" customHeight="1">
       <x:c r="A15" s="6" t="str">
@@ -574,9 +531,7 @@
       <x:c r="D15" s="6" t="str">
         <x:v>DID / SEG</x:v>
       </x:c>
-      <x:c r="E15" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E15" s="6"/>
     </x:row>
     <x:row r="16" ht="50" customHeight="1">
       <x:c r="A16" s="6" t="str">
@@ -591,9 +546,7 @@
       <x:c r="D16" s="6" t="str">
         <x:v>CTR / IT</x:v>
       </x:c>
-      <x:c r="E16" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E16" s="6"/>
     </x:row>
     <x:row r="17" ht="50" customHeight="1">
       <x:c r="A17" s="6" t="str">
@@ -608,9 +561,7 @@
       <x:c r="D17" s="6" t="str">
         <x:v>IT / TUT</x:v>
       </x:c>
-      <x:c r="E17" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E17" s="6"/>
     </x:row>
     <x:row r="18" ht="50" customHeight="1">
       <x:c r="A18" s="6" t="str">
@@ -625,9 +576,7 @@
       <x:c r="D18" s="6" t="str">
         <x:v>SEG</x:v>
       </x:c>
-      <x:c r="E18" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E18" s="6"/>
     </x:row>
     <x:row r="19" ht="50" customHeight="1">
       <x:c r="A19" s="6" t="str">
@@ -642,9 +591,7 @@
       <x:c r="D19" s="6" t="str">
         <x:v>SEG</x:v>
       </x:c>
-      <x:c r="E19" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E19" s="6"/>
     </x:row>
     <x:row r="20" ht="68" customHeight="1">
       <x:c r="A20" s="6" t="str">
@@ -659,9 +606,7 @@
       <x:c r="D20" s="6" t="str">
         <x:v>SEG / TUT</x:v>
       </x:c>
-      <x:c r="E20" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E20" s="6"/>
     </x:row>
     <x:row r="21" ht="50" customHeight="1">
       <x:c r="A21" s="6" t="str">
@@ -676,9 +621,7 @@
       <x:c r="D21" s="6" t="str">
         <x:v>DOC / TUT</x:v>
       </x:c>
-      <x:c r="E21" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E21" s="6"/>
     </x:row>
     <x:row r="22" ht="50" customHeight="1">
       <x:c r="A22" s="6" t="str">
@@ -693,9 +636,7 @@
       <x:c r="D22" s="6" t="str">
         <x:v>TUT / IT / SEG</x:v>
       </x:c>
-      <x:c r="E22" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E22" s="6"/>
     </x:row>
     <x:row r="23" ht="68" customHeight="1">
       <x:c r="A23" s="6" t="str">
@@ -710,9 +651,7 @@
       <x:c r="D23" s="6" t="str">
         <x:v>DOC / DID</x:v>
       </x:c>
-      <x:c r="E23" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E23" s="6"/>
     </x:row>
     <x:row r="24" ht="50" customHeight="1">
       <x:c r="A24" s="6" t="str">
@@ -727,9 +666,7 @@
       <x:c r="D24" s="6" t="str">
         <x:v>DID / SEG</x:v>
       </x:c>
-      <x:c r="E24" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E24" s="6"/>
     </x:row>
     <x:row r="25" ht="68" customHeight="1">
       <x:c r="A25" s="6" t="str">
@@ -744,9 +681,7 @@
       <x:c r="D25" s="6" t="str">
         <x:v>SEG</x:v>
       </x:c>
-      <x:c r="E25" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E25" s="6"/>
     </x:row>
     <x:row r="26" ht="50" customHeight="1">
       <x:c r="A26" s="6" t="str">
@@ -761,9 +696,7 @@
       <x:c r="D26" s="6" t="str">
         <x:v>SEG / DID</x:v>
       </x:c>
-      <x:c r="E26" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E26" s="6"/>
     </x:row>
     <x:row r="27" ht="50" customHeight="1">
       <x:c r="A27" s="6" t="str">
@@ -778,9 +711,7 @@
       <x:c r="D27" s="6" t="str">
         <x:v>QUAL / SEG / SOC</x:v>
       </x:c>
-      <x:c r="E27" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E27" s="6"/>
     </x:row>
     <x:row r="28" ht="68" customHeight="1">
       <x:c r="A28" s="6" t="str">
@@ -795,9 +726,7 @@
       <x:c r="D28" s="6" t="str">
         <x:v>AMM / DID / IT</x:v>
       </x:c>
-      <x:c r="E28" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E28" s="6"/>
     </x:row>
     <x:row r="29" ht="50" customHeight="1">
       <x:c r="A29" s="6" t="str">
@@ -812,9 +741,7 @@
       <x:c r="D29" s="6" t="str">
         <x:v>DIR / DID</x:v>
       </x:c>
-      <x:c r="E29" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E29" s="6"/>
     </x:row>
     <x:row r="30" ht="50" customHeight="1">
       <x:c r="A30" s="6" t="str">
@@ -829,9 +756,7 @@
       <x:c r="D30" s="6" t="str">
         <x:v>QUAL / DID</x:v>
       </x:c>
-      <x:c r="E30" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E30" s="6"/>
     </x:row>
     <x:row r="31" ht="50" customHeight="1">
       <x:c r="A31" s="6" t="str">
@@ -846,9 +771,7 @@
       <x:c r="D31" s="6" t="str">
         <x:v>QUAL / IT</x:v>
       </x:c>
-      <x:c r="E31" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E31" s="6"/>
     </x:row>
     <x:row r="32" ht="50" customHeight="1">
       <x:c r="A32" s="6" t="str">
@@ -863,9 +786,7 @@
       <x:c r="D32" s="6" t="str">
         <x:v>SOC / SEG</x:v>
       </x:c>
-      <x:c r="E32" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E32" s="6"/>
     </x:row>
     <x:row r="33" ht="50" customHeight="1">
       <x:c r="A33" s="6" t="str">
@@ -880,9 +801,7 @@
       <x:c r="D33" s="6" t="str">
         <x:v>QUAL / responsabile processo</x:v>
       </x:c>
-      <x:c r="E33" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E33" s="6"/>
     </x:row>
     <x:row r="34" ht="68" customHeight="1">
       <x:c r="A34" s="6" t="str">
@@ -897,9 +816,7 @@
       <x:c r="D34" s="6" t="str">
         <x:v>QUAL / responsabile processo</x:v>
       </x:c>
-      <x:c r="E34" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E34" s="6"/>
     </x:row>
     <x:row r="35" ht="50" customHeight="1">
       <x:c r="A35" s="6" t="str">
@@ -914,9 +831,7 @@
       <x:c r="D35" s="6" t="str">
         <x:v>QUAL</x:v>
       </x:c>
-      <x:c r="E35" s="6" t="str">
-        <x:v>Bozza da confermare</x:v>
-      </x:c>
+      <x:c r="E35" s="6"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36"/>
@@ -1367,6 +1282,5 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0968ed6569184eb5"/>
 </x:worksheet>
 </file>